--- a/data/Growth_Parameters.xlsx
+++ b/data/Growth_Parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-2204\home\yichen\SrRuO3_Plume_Dynamics\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yichen\Lehigh University Dropbox\Yichen Guo\SrRuO3_Plume_Dynamics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81D9D31-3047-4B45-8001-3422A18D6555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCE1B98-6D9C-4230-A4A9-9F1A8C09269F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18720" yWindow="336" windowWidth="21744" windowHeight="15828" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,7 +506,7 @@
     <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -824,6 +824,15 @@
       </c>
       <c r="K7" s="1">
         <v>12357</v>
+      </c>
+      <c r="L7" s="1">
+        <v>70.8</v>
+      </c>
+      <c r="M7" s="1">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1.71</v>
       </c>
       <c r="P7" s="1" t="s">
         <v>4</v>
